--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$305</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8630" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10910" uniqueCount="576">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>FrBundleDocument est utilisé pour représenter l'en-tête et le corps d'un document .</t>
+    <t>FrBundleDocument permet d’assembler les éléments de l’en-tête et du corps d’un document.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -570,7 +570,7 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>5</t>
+    <t>8</t>
   </si>
   <si>
     <t>Ressource Entry dans le FrBundleDocument</t>
@@ -885,7 +885,7 @@
     <t>Bundle.entry:composition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Composition {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-Composition-document}
+    <t xml:space="preserve">Composition {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document}
 </t>
   </si>
   <si>
@@ -1241,10 +1241,10 @@
 </t>
   </si>
   <si>
-    <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
-  </si>
-  <si>
-    <t>A person who is directly or indirectly involved in the provisioning of healthcare.</t>
+    <t>A person with a  formal responsibility in the provisioning of healthcare or related services | Prestataire de santé</t>
+  </si>
+  <si>
+    <t>A person who is directly or indirectly involved in the provisioning of healthcare | Un professionnel impliqué directement ou indirectement dans la prise en charge d'une personne.</t>
   </si>
   <si>
     <t>Bundle.entry:practitioner.search</t>
@@ -1346,7 +1346,7 @@
     <t>Bundle.entry:organization.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-Organization-document}
+    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document}
 </t>
   </si>
   <si>
@@ -1547,6 +1547,234 @@
   </si>
   <si>
     <t>Bundle.entry:device.response.outcome</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter</t>
+  </si>
+  <si>
+    <t>encounter</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encounter {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-encounter-document}
+</t>
+  </si>
+  <si>
+    <t>An interaction during which services are provided to the patient</t>
+  </si>
+  <si>
+    <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
+  </si>
+  <si>
+    <t>Encounter[@moodCode='EVN']</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:encounter.response.outcome</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-location-document}
+</t>
+  </si>
+  <si>
+    <t>Details and position information for a physical place</t>
+  </si>
+  <si>
+    <t>Details and position information for a physical place where services are provided and resources and participants may be stored, found, contained, or accommodated.</t>
+  </si>
+  <si>
+    <t>.Role[classCode=SDLC]</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:location.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1882,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN241"/>
+  <dimension ref="A1:AN305"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.328125" customWidth="true" bestFit="true"/>
@@ -11013,7 +11241,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>86</v>
@@ -26304,7 +26532,7 @@
         <v>77</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>76</v>
@@ -26986,7 +27214,7 @@
         <v>77</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>76</v>
@@ -28114,7 +28342,7 @@
         <v>77</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H232" t="s" s="2">
         <v>76</v>
@@ -29123,18 +29351,20 @@
         <v>495</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C241" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="C241" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="D241" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G241" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H241" t="s" s="2">
         <v>76</v>
@@ -29146,20 +29376,16 @@
         <v>87</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>496</v>
+        <v>144</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>497</v>
+        <v>268</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N241" s="2"/>
+      <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>76</v>
       </c>
@@ -29207,35 +29433,7285 @@
         <v>76</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>495</v>
+        <v>174</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH241" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI241" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ241" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AK241" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL241" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM241" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN241" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="242" hidden="true">
+      <c r="A242" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C242" s="2"/>
+      <c r="D242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E242" s="2"/>
+      <c r="F242" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G242" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K242" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L242" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M242" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N242" s="2"/>
+      <c r="O242" s="2"/>
+      <c r="P242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q242" s="2"/>
+      <c r="R242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF242" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG242" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH242" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL242" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM242" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN242" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="243" hidden="true">
+      <c r="A243" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C243" s="2"/>
+      <c r="D243" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E243" s="2"/>
+      <c r="F243" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G243" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K243" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L243" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M243" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N243" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O243" s="2"/>
+      <c r="P243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q243" s="2"/>
+      <c r="R243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF243" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG243" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH243" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ243" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL243" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM243" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN243" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="244" hidden="true">
+      <c r="A244" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C244" s="2"/>
+      <c r="D244" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E244" s="2"/>
+      <c r="F244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G244" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I244" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J244" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K244" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L244" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M244" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N244" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O244" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q244" s="2"/>
+      <c r="R244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF244" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH244" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ244" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL244" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM244" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN244" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="245" hidden="true">
+      <c r="A245" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C245" s="2"/>
+      <c r="D245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E245" s="2"/>
+      <c r="F245" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G245" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J245" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L245" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M245" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N245" s="2"/>
+      <c r="O245" s="2"/>
+      <c r="P245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q245" s="2"/>
+      <c r="R245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF245" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG245" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH245" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ245" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AK241" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL241" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM241" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN241" t="s" s="2">
+      <c r="AK245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM245" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN245" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="246" hidden="true">
+      <c r="A246" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C246" s="2"/>
+      <c r="D246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E246" s="2"/>
+      <c r="F246" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G246" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H246" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J246" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K246" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L246" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M246" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N246" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O246" s="2"/>
+      <c r="P246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q246" s="2"/>
+      <c r="R246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF246" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG246" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH246" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ246" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM246" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN246" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="247" hidden="true">
+      <c r="A247" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="E247" s="2"/>
+      <c r="F247" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G247" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K247" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L247" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M247" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N247" s="2"/>
+      <c r="O247" s="2"/>
+      <c r="P247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q247" s="2"/>
+      <c r="R247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF247" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG247" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH247" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL247" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AM247" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN247" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="248" hidden="true">
+      <c r="A248" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E248" s="2"/>
+      <c r="F248" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G248" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J248" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K248" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L248" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M248" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N248" s="2"/>
+      <c r="O248" s="2"/>
+      <c r="P248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q248" s="2"/>
+      <c r="R248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF248" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG248" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH248" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI248" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AJ248" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM248" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN248" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="249" hidden="true">
+      <c r="A249" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C249" s="2"/>
+      <c r="D249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E249" s="2"/>
+      <c r="F249" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G249" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K249" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L249" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M249" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N249" s="2"/>
+      <c r="O249" s="2"/>
+      <c r="P249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q249" s="2"/>
+      <c r="R249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF249" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG249" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH249" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL249" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM249" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN249" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="250" hidden="true">
+      <c r="A250" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E250" s="2"/>
+      <c r="F250" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G250" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K250" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L250" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M250" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N250" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O250" s="2"/>
+      <c r="P250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q250" s="2"/>
+      <c r="R250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF250" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG250" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH250" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ250" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL250" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM250" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN250" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="251" hidden="true">
+      <c r="A251" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C251" s="2"/>
+      <c r="D251" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E251" s="2"/>
+      <c r="F251" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I251" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J251" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K251" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L251" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M251" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N251" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O251" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q251" s="2"/>
+      <c r="R251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF251" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG251" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ251" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL251" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM251" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN251" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="252" hidden="true">
+      <c r="A252" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C252" s="2"/>
+      <c r="D252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E252" s="2"/>
+      <c r="F252" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G252" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J252" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K252" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L252" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M252" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N252" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O252" s="2"/>
+      <c r="P252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q252" s="2"/>
+      <c r="R252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X252" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y252" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z252" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF252" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG252" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH252" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ252" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN252" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="253" hidden="true">
+      <c r="A253" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C253" s="2"/>
+      <c r="D253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E253" s="2"/>
+      <c r="F253" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G253" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J253" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K253" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L253" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M253" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N253" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O253" s="2"/>
+      <c r="P253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q253" s="2"/>
+      <c r="R253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF253" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG253" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH253" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ253" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN253" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="254" hidden="true">
+      <c r="A254" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C254" s="2"/>
+      <c r="D254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E254" s="2"/>
+      <c r="F254" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G254" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J254" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K254" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L254" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M254" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N254" s="2"/>
+      <c r="O254" s="2"/>
+      <c r="P254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q254" s="2"/>
+      <c r="R254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF254" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG254" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH254" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI254" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AJ254" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM254" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN254" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="255" hidden="true">
+      <c r="A255" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C255" s="2"/>
+      <c r="D255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E255" s="2"/>
+      <c r="F255" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G255" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K255" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L255" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M255" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N255" s="2"/>
+      <c r="O255" s="2"/>
+      <c r="P255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q255" s="2"/>
+      <c r="R255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF255" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG255" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH255" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL255" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM255" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN255" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="256" hidden="true">
+      <c r="A256" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C256" s="2"/>
+      <c r="D256" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E256" s="2"/>
+      <c r="F256" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G256" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K256" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L256" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M256" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N256" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O256" s="2"/>
+      <c r="P256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q256" s="2"/>
+      <c r="R256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF256" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG256" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH256" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ256" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL256" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM256" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN256" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="257" hidden="true">
+      <c r="A257" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C257" s="2"/>
+      <c r="D257" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E257" s="2"/>
+      <c r="F257" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G257" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I257" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J257" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K257" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L257" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M257" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N257" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O257" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q257" s="2"/>
+      <c r="R257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF257" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG257" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH257" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ257" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL257" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM257" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN257" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="258" hidden="true">
+      <c r="A258" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C258" s="2"/>
+      <c r="D258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E258" s="2"/>
+      <c r="F258" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G258" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J258" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K258" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L258" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M258" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N258" s="2"/>
+      <c r="O258" s="2"/>
+      <c r="P258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q258" s="2"/>
+      <c r="R258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X258" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y258" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z258" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF258" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG258" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH258" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ258" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM258" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN258" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="259" hidden="true">
+      <c r="A259" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C259" s="2"/>
+      <c r="D259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E259" s="2"/>
+      <c r="F259" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G259" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J259" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K259" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L259" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M259" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N259" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O259" s="2"/>
+      <c r="P259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q259" s="2"/>
+      <c r="R259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF259" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG259" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH259" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ259" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM259" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN259" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="260" hidden="true">
+      <c r="A260" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C260" s="2"/>
+      <c r="D260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E260" s="2"/>
+      <c r="F260" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G260" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J260" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K260" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L260" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M260" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N260" s="2"/>
+      <c r="O260" s="2"/>
+      <c r="P260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q260" s="2"/>
+      <c r="R260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF260" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG260" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH260" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ260" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM260" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN260" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="261" hidden="true">
+      <c r="A261" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C261" s="2"/>
+      <c r="D261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E261" s="2"/>
+      <c r="F261" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G261" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J261" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K261" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L261" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M261" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N261" s="2"/>
+      <c r="O261" s="2"/>
+      <c r="P261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q261" s="2"/>
+      <c r="R261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF261" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG261" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH261" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ261" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM261" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN261" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="262" hidden="true">
+      <c r="A262" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C262" s="2"/>
+      <c r="D262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E262" s="2"/>
+      <c r="F262" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G262" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J262" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K262" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L262" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M262" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N262" s="2"/>
+      <c r="O262" s="2"/>
+      <c r="P262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q262" s="2"/>
+      <c r="R262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF262" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG262" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH262" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ262" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM262" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN262" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="263" hidden="true">
+      <c r="A263" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C263" s="2"/>
+      <c r="D263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E263" s="2"/>
+      <c r="F263" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G263" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J263" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K263" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L263" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M263" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N263" s="2"/>
+      <c r="O263" s="2"/>
+      <c r="P263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q263" s="2"/>
+      <c r="R263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF263" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG263" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH263" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ263" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM263" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN263" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="264" hidden="true">
+      <c r="A264" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C264" s="2"/>
+      <c r="D264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E264" s="2"/>
+      <c r="F264" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G264" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J264" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K264" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L264" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M264" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N264" s="2"/>
+      <c r="O264" s="2"/>
+      <c r="P264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q264" s="2"/>
+      <c r="R264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF264" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG264" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH264" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI264" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AJ264" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM264" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN264" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="265" hidden="true">
+      <c r="A265" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C265" s="2"/>
+      <c r="D265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E265" s="2"/>
+      <c r="F265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G265" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K265" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L265" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M265" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N265" s="2"/>
+      <c r="O265" s="2"/>
+      <c r="P265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q265" s="2"/>
+      <c r="R265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF265" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH265" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL265" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM265" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN265" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="266" hidden="true">
+      <c r="A266" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C266" s="2"/>
+      <c r="D266" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E266" s="2"/>
+      <c r="F266" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G266" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K266" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L266" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M266" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N266" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O266" s="2"/>
+      <c r="P266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q266" s="2"/>
+      <c r="R266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF266" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG266" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH266" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ266" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL266" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM266" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN266" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="267" hidden="true">
+      <c r="A267" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C267" s="2"/>
+      <c r="D267" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E267" s="2"/>
+      <c r="F267" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G267" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I267" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J267" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K267" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L267" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M267" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N267" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O267" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q267" s="2"/>
+      <c r="R267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF267" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG267" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH267" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ267" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL267" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM267" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN267" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="268" hidden="true">
+      <c r="A268" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C268" s="2"/>
+      <c r="D268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E268" s="2"/>
+      <c r="F268" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G268" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J268" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K268" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L268" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M268" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N268" s="2"/>
+      <c r="O268" s="2"/>
+      <c r="P268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q268" s="2"/>
+      <c r="R268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF268" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG268" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH268" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ268" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM268" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN268" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="269" hidden="true">
+      <c r="A269" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C269" s="2"/>
+      <c r="D269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E269" s="2"/>
+      <c r="F269" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G269" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J269" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K269" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L269" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M269" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N269" s="2"/>
+      <c r="O269" s="2"/>
+      <c r="P269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q269" s="2"/>
+      <c r="R269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF269" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG269" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH269" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ269" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM269" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN269" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="270" hidden="true">
+      <c r="A270" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C270" s="2"/>
+      <c r="D270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E270" s="2"/>
+      <c r="F270" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G270" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J270" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K270" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L270" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M270" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N270" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O270" s="2"/>
+      <c r="P270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q270" s="2"/>
+      <c r="R270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF270" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG270" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH270" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ270" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM270" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN270" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="271" hidden="true">
+      <c r="A271" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C271" s="2"/>
+      <c r="D271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E271" s="2"/>
+      <c r="F271" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G271" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J271" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K271" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L271" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M271" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N271" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O271" s="2"/>
+      <c r="P271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q271" s="2"/>
+      <c r="R271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF271" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG271" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH271" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ271" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM271" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN271" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="272" hidden="true">
+      <c r="A272" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C272" s="2"/>
+      <c r="D272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E272" s="2"/>
+      <c r="F272" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G272" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J272" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K272" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L272" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M272" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O272" s="2"/>
+      <c r="P272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q272" s="2"/>
+      <c r="R272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF272" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG272" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH272" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM272" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN272" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="273" hidden="true">
+      <c r="A273" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C273" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="D273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E273" s="2"/>
+      <c r="F273" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J273" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K273" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L273" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M273" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N273" s="2"/>
+      <c r="O273" s="2"/>
+      <c r="P273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q273" s="2"/>
+      <c r="R273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF273" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG273" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ273" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AK273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM273" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN273" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="274" hidden="true">
+      <c r="A274" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C274" s="2"/>
+      <c r="D274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E274" s="2"/>
+      <c r="F274" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G274" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K274" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L274" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M274" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N274" s="2"/>
+      <c r="O274" s="2"/>
+      <c r="P274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q274" s="2"/>
+      <c r="R274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF274" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG274" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH274" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL274" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM274" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN274" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="275" hidden="true">
+      <c r="A275" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C275" s="2"/>
+      <c r="D275" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E275" s="2"/>
+      <c r="F275" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G275" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K275" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L275" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M275" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N275" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O275" s="2"/>
+      <c r="P275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q275" s="2"/>
+      <c r="R275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF275" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG275" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH275" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ275" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL275" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM275" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN275" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="276" hidden="true">
+      <c r="A276" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C276" s="2"/>
+      <c r="D276" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E276" s="2"/>
+      <c r="F276" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G276" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I276" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J276" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K276" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L276" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M276" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N276" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O276" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q276" s="2"/>
+      <c r="R276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF276" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG276" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH276" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ276" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL276" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM276" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN276" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="277" hidden="true">
+      <c r="A277" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C277" s="2"/>
+      <c r="D277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E277" s="2"/>
+      <c r="F277" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G277" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J277" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K277" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L277" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M277" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N277" s="2"/>
+      <c r="O277" s="2"/>
+      <c r="P277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q277" s="2"/>
+      <c r="R277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF277" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG277" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH277" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ277" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM277" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN277" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="278" hidden="true">
+      <c r="A278" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B278" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C278" s="2"/>
+      <c r="D278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E278" s="2"/>
+      <c r="F278" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G278" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H278" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J278" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K278" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L278" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M278" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N278" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O278" s="2"/>
+      <c r="P278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q278" s="2"/>
+      <c r="R278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF278" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG278" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH278" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ278" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM278" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN278" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="279" hidden="true">
+      <c r="A279" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B279" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C279" s="2"/>
+      <c r="D279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E279" s="2"/>
+      <c r="F279" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G279" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K279" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L279" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M279" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N279" s="2"/>
+      <c r="O279" s="2"/>
+      <c r="P279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q279" s="2"/>
+      <c r="R279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF279" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG279" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH279" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL279" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM279" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN279" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="280" hidden="true">
+      <c r="A280" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C280" s="2"/>
+      <c r="D280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E280" s="2"/>
+      <c r="F280" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G280" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J280" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K280" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L280" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M280" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N280" s="2"/>
+      <c r="O280" s="2"/>
+      <c r="P280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q280" s="2"/>
+      <c r="R280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF280" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG280" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH280" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI280" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AJ280" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM280" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN280" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="281" hidden="true">
+      <c r="A281" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C281" s="2"/>
+      <c r="D281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E281" s="2"/>
+      <c r="F281" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G281" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K281" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L281" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M281" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N281" s="2"/>
+      <c r="O281" s="2"/>
+      <c r="P281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q281" s="2"/>
+      <c r="R281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF281" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG281" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH281" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL281" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM281" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN281" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="282" hidden="true">
+      <c r="A282" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C282" s="2"/>
+      <c r="D282" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E282" s="2"/>
+      <c r="F282" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G282" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K282" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L282" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M282" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N282" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O282" s="2"/>
+      <c r="P282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q282" s="2"/>
+      <c r="R282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF282" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG282" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH282" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ282" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL282" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM282" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN282" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="283" hidden="true">
+      <c r="A283" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C283" s="2"/>
+      <c r="D283" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E283" s="2"/>
+      <c r="F283" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G283" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I283" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J283" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K283" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L283" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M283" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N283" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O283" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q283" s="2"/>
+      <c r="R283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF283" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG283" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH283" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ283" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL283" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM283" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN283" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="284" hidden="true">
+      <c r="A284" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C284" s="2"/>
+      <c r="D284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E284" s="2"/>
+      <c r="F284" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G284" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J284" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K284" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L284" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M284" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N284" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O284" s="2"/>
+      <c r="P284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q284" s="2"/>
+      <c r="R284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X284" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y284" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z284" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF284" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG284" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH284" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ284" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM284" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN284" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="285" hidden="true">
+      <c r="A285" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C285" s="2"/>
+      <c r="D285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E285" s="2"/>
+      <c r="F285" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G285" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J285" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K285" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L285" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M285" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N285" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O285" s="2"/>
+      <c r="P285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q285" s="2"/>
+      <c r="R285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF285" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG285" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH285" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ285" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM285" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN285" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="286" hidden="true">
+      <c r="A286" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C286" s="2"/>
+      <c r="D286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E286" s="2"/>
+      <c r="F286" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G286" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J286" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K286" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L286" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M286" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N286" s="2"/>
+      <c r="O286" s="2"/>
+      <c r="P286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q286" s="2"/>
+      <c r="R286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF286" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG286" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH286" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI286" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AJ286" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM286" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN286" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="287" hidden="true">
+      <c r="A287" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C287" s="2"/>
+      <c r="D287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E287" s="2"/>
+      <c r="F287" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G287" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K287" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L287" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M287" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N287" s="2"/>
+      <c r="O287" s="2"/>
+      <c r="P287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q287" s="2"/>
+      <c r="R287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF287" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG287" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH287" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL287" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN287" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="288" hidden="true">
+      <c r="A288" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C288" s="2"/>
+      <c r="D288" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E288" s="2"/>
+      <c r="F288" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G288" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K288" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L288" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M288" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N288" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O288" s="2"/>
+      <c r="P288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q288" s="2"/>
+      <c r="R288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF288" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG288" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH288" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ288" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL288" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM288" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN288" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="289" hidden="true">
+      <c r="A289" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C289" s="2"/>
+      <c r="D289" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E289" s="2"/>
+      <c r="F289" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G289" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I289" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J289" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K289" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L289" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M289" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N289" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O289" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q289" s="2"/>
+      <c r="R289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF289" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG289" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH289" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ289" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM289" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN289" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="290" hidden="true">
+      <c r="A290" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C290" s="2"/>
+      <c r="D290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E290" s="2"/>
+      <c r="F290" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G290" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J290" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K290" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L290" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M290" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N290" s="2"/>
+      <c r="O290" s="2"/>
+      <c r="P290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q290" s="2"/>
+      <c r="R290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X290" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y290" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z290" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF290" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG290" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH290" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ290" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM290" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN290" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="291" hidden="true">
+      <c r="A291" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C291" s="2"/>
+      <c r="D291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E291" s="2"/>
+      <c r="F291" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G291" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J291" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K291" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L291" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M291" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N291" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O291" s="2"/>
+      <c r="P291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q291" s="2"/>
+      <c r="R291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF291" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG291" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH291" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ291" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM291" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN291" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="292" hidden="true">
+      <c r="A292" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C292" s="2"/>
+      <c r="D292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E292" s="2"/>
+      <c r="F292" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G292" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J292" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K292" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L292" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M292" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N292" s="2"/>
+      <c r="O292" s="2"/>
+      <c r="P292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q292" s="2"/>
+      <c r="R292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF292" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG292" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH292" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ292" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM292" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN292" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="293" hidden="true">
+      <c r="A293" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C293" s="2"/>
+      <c r="D293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E293" s="2"/>
+      <c r="F293" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G293" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J293" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K293" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L293" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M293" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N293" s="2"/>
+      <c r="O293" s="2"/>
+      <c r="P293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q293" s="2"/>
+      <c r="R293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF293" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG293" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH293" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ293" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM293" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN293" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="294" hidden="true">
+      <c r="A294" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C294" s="2"/>
+      <c r="D294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E294" s="2"/>
+      <c r="F294" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G294" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J294" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K294" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L294" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M294" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N294" s="2"/>
+      <c r="O294" s="2"/>
+      <c r="P294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q294" s="2"/>
+      <c r="R294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF294" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG294" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH294" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ294" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM294" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN294" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="295" hidden="true">
+      <c r="A295" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C295" s="2"/>
+      <c r="D295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E295" s="2"/>
+      <c r="F295" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G295" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J295" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K295" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L295" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M295" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N295" s="2"/>
+      <c r="O295" s="2"/>
+      <c r="P295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q295" s="2"/>
+      <c r="R295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF295" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG295" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH295" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ295" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM295" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN295" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="296" hidden="true">
+      <c r="A296" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C296" s="2"/>
+      <c r="D296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E296" s="2"/>
+      <c r="F296" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G296" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J296" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K296" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L296" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M296" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N296" s="2"/>
+      <c r="O296" s="2"/>
+      <c r="P296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q296" s="2"/>
+      <c r="R296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF296" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG296" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH296" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI296" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AJ296" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM296" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN296" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="297" hidden="true">
+      <c r="A297" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C297" s="2"/>
+      <c r="D297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E297" s="2"/>
+      <c r="F297" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G297" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K297" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L297" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M297" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N297" s="2"/>
+      <c r="O297" s="2"/>
+      <c r="P297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q297" s="2"/>
+      <c r="R297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF297" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG297" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH297" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL297" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM297" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN297" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="298" hidden="true">
+      <c r="A298" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C298" s="2"/>
+      <c r="D298" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E298" s="2"/>
+      <c r="F298" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G298" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K298" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L298" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M298" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N298" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O298" s="2"/>
+      <c r="P298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q298" s="2"/>
+      <c r="R298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF298" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG298" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH298" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ298" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL298" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM298" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN298" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="299" hidden="true">
+      <c r="A299" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C299" s="2"/>
+      <c r="D299" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E299" s="2"/>
+      <c r="F299" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G299" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I299" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J299" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K299" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L299" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M299" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N299" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O299" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q299" s="2"/>
+      <c r="R299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF299" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG299" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH299" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ299" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL299" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM299" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN299" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="300" hidden="true">
+      <c r="A300" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B300" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C300" s="2"/>
+      <c r="D300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E300" s="2"/>
+      <c r="F300" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G300" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J300" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K300" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L300" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M300" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N300" s="2"/>
+      <c r="O300" s="2"/>
+      <c r="P300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q300" s="2"/>
+      <c r="R300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF300" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG300" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH300" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ300" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM300" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN300" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="301" hidden="true">
+      <c r="A301" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B301" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C301" s="2"/>
+      <c r="D301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E301" s="2"/>
+      <c r="F301" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G301" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J301" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K301" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L301" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M301" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N301" s="2"/>
+      <c r="O301" s="2"/>
+      <c r="P301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q301" s="2"/>
+      <c r="R301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF301" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG301" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH301" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ301" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM301" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN301" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="302" hidden="true">
+      <c r="A302" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B302" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C302" s="2"/>
+      <c r="D302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E302" s="2"/>
+      <c r="F302" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G302" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J302" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K302" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L302" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M302" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N302" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O302" s="2"/>
+      <c r="P302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q302" s="2"/>
+      <c r="R302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF302" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG302" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH302" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ302" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM302" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN302" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="303" hidden="true">
+      <c r="A303" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C303" s="2"/>
+      <c r="D303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E303" s="2"/>
+      <c r="F303" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G303" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J303" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K303" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L303" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M303" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N303" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O303" s="2"/>
+      <c r="P303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q303" s="2"/>
+      <c r="R303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF303" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG303" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH303" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ303" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM303" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN303" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="304" hidden="true">
+      <c r="A304" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C304" s="2"/>
+      <c r="D304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E304" s="2"/>
+      <c r="F304" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G304" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J304" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K304" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L304" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M304" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N304" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O304" s="2"/>
+      <c r="P304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q304" s="2"/>
+      <c r="R304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF304" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG304" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH304" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM304" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN304" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="305" hidden="true">
+      <c r="A305" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C305" s="2"/>
+      <c r="D305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E305" s="2"/>
+      <c r="F305" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G305" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J305" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K305" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L305" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M305" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N305" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O305" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q305" s="2"/>
+      <c r="R305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF305" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG305" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH305" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ305" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM305" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AN305" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN241">
+  <autoFilter ref="A1:AN305">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -29245,7 +36721,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI240">
+  <conditionalFormatting sqref="A2:AI304">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>FrBundleDocument permet d’assembler les éléments de l’en-tête et du corps d’un document.</t>
+    <t>Ce profil permet d’assembler les éléments de l’en-tête et du corps d’un document.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4786,7 +4786,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -5468,7 +5468,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -6596,7 +6596,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -33780,7 +33780,7 @@
         <v>77</v>
       </c>
       <c r="G280" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H280" t="s" s="2">
         <v>76</v>
@@ -34462,7 +34462,7 @@
         <v>77</v>
       </c>
       <c r="G286" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H286" t="s" s="2">
         <v>76</v>
@@ -35590,7 +35590,7 @@
         <v>77</v>
       </c>
       <c r="G296" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H296" t="s" s="2">
         <v>76</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -573,7 +573,7 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>9</t>
+    <t>8</t>
   </si>
   <si>
     <t>Ressource Entry dans le FrBundleDocument</t>
@@ -3116,10 +3116,10 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="S8" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="T8" t="s" s="2">
         <v>77</v>
@@ -25852,10 +25852,10 @@
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>77</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,10 +262,10 @@
 </t>
   </si>
   <si>
-    <t>Bundle Document</t>
-  </si>
-  <si>
-    <t>Bundle Document.</t>
+    <t>Contains a collection of resources</t>
+  </si>
+  <si>
+    <t>A container for a collection of resources.</t>
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
@@ -573,7 +573,7 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>8</t>
+    <t>7</t>
   </si>
   <si>
     <t>Ressource Entry dans le FrBundleDocument</t>
@@ -892,10 +892,10 @@
 </t>
   </si>
   <si>
-    <t>Clinical document</t>
-  </si>
-  <si>
-    <t>Clinical document.</t>
+    <t>A set of resources composed into a single coherent clinical statement with clinical attestation</t>
+  </si>
+  <si>
+    <t>A set of healthcare-related information that is assembled together into a single logical package that provides a single coherent statement of meaning, establishes its own context and that has clinical attestation with regard to who is making the statement. A Composition defines the structure and narrative content necessary for a document. However, a Composition alone does not constitute a document. Rather, the Composition must be the first entry in a Bundle where Bundle.type=document, and any other resources referenced from Composition must be included as subsequent entries in the Bundle (for example Patient, Practitioner, Encounter, etc.).</t>
   </si>
   <si>
     <t>While the focus of this specification is on patient-specific clinical statements, this resource can also apply to other healthcare-related statements such as study protocol designs, healthcare invoices and other activities that are not necessarily patient-specific or clinical.</t>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="E305" s="2"/>
       <c r="F305" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G305" t="s" s="2">
         <v>79</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1010,7 +1010,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document}
+    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document}
 </t>
   </si>
   <si>
@@ -2228,17 +2228,17 @@
   <dimension ref="A1:AN337"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.0078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.74609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="28.78515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.44140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.5" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="24.67578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.7734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="151.15234375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2247,26 +2247,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.98046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="144.1953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="31.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="67.23828125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.9765625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="57.64453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
